--- a/pregenerated_results/ate_iptw_gee_IPTW_GEE_workload_index_mgr.xlsx
+++ b/pregenerated_results/ate_iptw_gee_IPTW_GEE_workload_index_mgr.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -564,10 +564,10 @@
         <v>0.046</v>
       </c>
       <c r="D5" t="n">
-        <v>0.011</v>
+        <v>0.01</v>
       </c>
       <c r="E5" t="n">
-        <v>0.035</v>
+        <v>0.036</v>
       </c>
       <c r="F5" t="b">
         <v>1</v>
@@ -591,10 +591,10 @@
         <v>0.097</v>
       </c>
       <c r="D6" t="n">
-        <v>0.021</v>
+        <v>0.02</v>
       </c>
       <c r="E6" t="n">
-        <v>0.076</v>
+        <v>0.077</v>
       </c>
       <c r="F6" t="b">
         <v>1</v>
@@ -606,7 +606,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>gender_Male</t>
+          <t>organization_Manufacturing</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -615,16 +615,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>-0.024</v>
+        <v>-0.128</v>
       </c>
       <c r="D7" t="n">
-        <v>0.027</v>
+        <v>0.019</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.002999999999999999</v>
+        <v>0.109</v>
       </c>
       <c r="F7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" t="b">
         <v>1</v>
@@ -633,7 +633,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>gender_Non_Binary_Other</t>
+          <t>job_family_Pharmacovigilance</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -642,13 +642,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.046</v>
+        <v>-0</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.002</v>
+        <v>-0.004</v>
       </c>
       <c r="E8" t="n">
-        <v>0.044</v>
+        <v>-0.004</v>
       </c>
       <c r="F8" t="b">
         <v>1</v>
@@ -660,7 +660,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>job_family_Communications</t>
+          <t>region_Europe</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -669,16 +669,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-0.008999999999999999</v>
+        <v>0.107</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.001</v>
+        <v>0.042</v>
       </c>
       <c r="E9" t="n">
-        <v>0.008</v>
+        <v>0.065</v>
       </c>
       <c r="F9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" t="b">
         <v>1</v>
@@ -687,7 +687,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>job_family_Data_Science</t>
+          <t>job_family_Finance_and_Accounting</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -696,13 +696,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>-0.074</v>
+        <v>0.034</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.042</v>
+        <v>-0.008</v>
       </c>
       <c r="E10" t="n">
-        <v>0.03199999999999999</v>
+        <v>0.026</v>
       </c>
       <c r="F10" t="b">
         <v>1</v>
@@ -714,7 +714,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>job_family_Finance_and_Accounting</t>
+          <t>performance_rating_Far_Exceeds</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -723,16 +723,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.034</v>
+        <v>0.392</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.008</v>
+        <v>0.03</v>
       </c>
       <c r="E11" t="n">
-        <v>0.026</v>
+        <v>0.362</v>
       </c>
       <c r="F11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11" t="b">
         <v>1</v>
@@ -768,7 +768,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>job_family_IT_and_Digital</t>
+          <t>job_family_Legal_and_Compliance</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -777,13 +777,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.007</v>
+        <v>0.041</v>
       </c>
       <c r="D13" t="n">
-        <v>0.025</v>
+        <v>0.038</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.018</v>
+        <v>0.003000000000000003</v>
       </c>
       <c r="F13" t="b">
         <v>1</v>
@@ -795,7 +795,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>job_family_Legal_and_Compliance</t>
+          <t>organization_HR</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -804,13 +804,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.041</v>
+        <v>-0.054</v>
       </c>
       <c r="D14" t="n">
-        <v>0.038</v>
+        <v>-0.028</v>
       </c>
       <c r="E14" t="n">
-        <v>0.003000000000000003</v>
+        <v>0.026</v>
       </c>
       <c r="F14" t="b">
         <v>1</v>
@@ -822,7 +822,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>job_family_Market_Access</t>
+          <t>job_family_Quality_Assurance</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -831,13 +831,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.005</v>
+        <v>-0.008</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.013</v>
+        <v>-0</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.008</v>
+        <v>0.008</v>
       </c>
       <c r="F15" t="b">
         <v>1</v>
@@ -849,7 +849,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>job_family_Marketing</t>
+          <t>performance_rating_Meets</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -858,16 +858,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.032</v>
+        <v>-0.401</v>
       </c>
       <c r="D16" t="n">
-        <v>0.03</v>
+        <v>-0.037</v>
       </c>
       <c r="E16" t="n">
-        <v>0.002000000000000002</v>
+        <v>0.364</v>
       </c>
       <c r="F16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G16" t="b">
         <v>1</v>
@@ -876,7 +876,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>job_family_Medical_Affairs</t>
+          <t>job_family_IT_and_Digital</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -885,13 +885,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>-0.014</v>
+        <v>0.007</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.003</v>
+        <v>0.026</v>
       </c>
       <c r="E17" t="n">
-        <v>0.011</v>
+        <v>-0.019</v>
       </c>
       <c r="F17" t="b">
         <v>1</v>
@@ -903,7 +903,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>job_family_Pharmacovigilance</t>
+          <t>job_family_Market_Access</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -912,13 +912,13 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>-0</v>
+        <v>0.005</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.004</v>
+        <v>-0.013</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.004</v>
+        <v>-0.008</v>
       </c>
       <c r="F18" t="b">
         <v>1</v>
@@ -930,7 +930,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>job_family_Quality_Assurance</t>
+          <t>job_family_Supply_Chain</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -939,16 +939,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>-0.008</v>
+        <v>-0.113</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.001</v>
+        <v>-0.05</v>
       </c>
       <c r="E19" t="n">
-        <v>0.007</v>
+        <v>0.063</v>
       </c>
       <c r="F19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G19" t="b">
         <v>1</v>
@@ -957,7 +957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>job_family_Regulatory_Affairs</t>
+          <t>organization_Finance</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -966,16 +966,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.077</v>
+        <v>-0.143</v>
       </c>
       <c r="D20" t="n">
-        <v>0.031</v>
+        <v>-0.042</v>
       </c>
       <c r="E20" t="n">
-        <v>0.046</v>
+        <v>0.101</v>
       </c>
       <c r="F20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G20" t="b">
         <v>1</v>
@@ -984,7 +984,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>job_family_Sales</t>
+          <t>gender_Male</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -993,13 +993,13 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>-0.019</v>
+        <v>-0.024</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.023</v>
+        <v>0.027</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.004</v>
+        <v>-0.002999999999999999</v>
       </c>
       <c r="F21" t="b">
         <v>1</v>
@@ -1011,7 +1011,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>job_family_Supply_Chain</t>
+          <t>job_family_Marketing</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1020,16 +1020,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>-0.113</v>
+        <v>0.032</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.05</v>
+        <v>0.03</v>
       </c>
       <c r="E22" t="n">
-        <v>0.063</v>
+        <v>0.002000000000000002</v>
       </c>
       <c r="F22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G22" t="b">
         <v>1</v>
@@ -1038,7 +1038,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>organization_Digital</t>
+          <t>region_North_America</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1047,16 +1047,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.197</v>
+        <v>0.022</v>
       </c>
       <c r="D23" t="n">
-        <v>0.065</v>
+        <v>0.014</v>
       </c>
       <c r="E23" t="n">
-        <v>0.132</v>
+        <v>0.007999999999999998</v>
       </c>
       <c r="F23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G23" t="b">
         <v>1</v>
@@ -1065,7 +1065,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>organization_Finance</t>
+          <t>organization_RandD</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1074,13 +1074,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>-0.143</v>
+        <v>0.227</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.042</v>
+        <v>0.021</v>
       </c>
       <c r="E24" t="n">
-        <v>0.101</v>
+        <v>0.206</v>
       </c>
       <c r="F24" t="b">
         <v>0</v>
@@ -1092,7 +1092,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>organization_HR</t>
+          <t>gender_Non_Binary_Other</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1101,13 +1101,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>-0.054</v>
+        <v>0.046</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.027</v>
+        <v>-0.002</v>
       </c>
       <c r="E25" t="n">
-        <v>0.027</v>
+        <v>0.044</v>
       </c>
       <c r="F25" t="b">
         <v>1</v>
@@ -1119,7 +1119,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>organization_Manufacturing</t>
+          <t>job_family_Regulatory_Affairs</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1128,16 +1128,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>-0.128</v>
+        <v>0.077</v>
       </c>
       <c r="D26" t="n">
-        <v>0.019</v>
+        <v>0.03</v>
       </c>
       <c r="E26" t="n">
-        <v>0.109</v>
+        <v>0.047</v>
       </c>
       <c r="F26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G26" t="b">
         <v>1</v>
@@ -1146,7 +1146,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>organization_RandD</t>
+          <t>job_family_Medical_Affairs</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1155,16 +1155,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.227</v>
+        <v>-0.014</v>
       </c>
       <c r="D27" t="n">
-        <v>0.022</v>
+        <v>-0.003</v>
       </c>
       <c r="E27" t="n">
-        <v>0.205</v>
+        <v>0.011</v>
       </c>
       <c r="F27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G27" t="b">
         <v>1</v>
@@ -1173,7 +1173,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>performance_rating_Far_Exceeds</t>
+          <t>organization_Digital</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1182,13 +1182,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.392</v>
+        <v>0.197</v>
       </c>
       <c r="D28" t="n">
-        <v>0.03</v>
+        <v>0.065</v>
       </c>
       <c r="E28" t="n">
-        <v>0.362</v>
+        <v>0.132</v>
       </c>
       <c r="F28" t="b">
         <v>0</v>
@@ -1200,7 +1200,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>performance_rating_Meets</t>
+          <t>job_family_Data_Science</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1209,16 +1209,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>-0.401</v>
+        <v>-0.074</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.038</v>
+        <v>-0.042</v>
       </c>
       <c r="E29" t="n">
-        <v>0.363</v>
+        <v>0.03199999999999999</v>
       </c>
       <c r="F29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G29" t="b">
         <v>1</v>
@@ -1227,7 +1227,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>region_Europe</t>
+          <t>region_Latin_America</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1236,16 +1236,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.107</v>
+        <v>-0.041</v>
       </c>
       <c r="D30" t="n">
-        <v>0.042</v>
+        <v>-0.012</v>
       </c>
       <c r="E30" t="n">
-        <v>0.065</v>
+        <v>0.029</v>
       </c>
       <c r="F30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G30" t="b">
         <v>1</v>
@@ -1254,7 +1254,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>region_Latin_America</t>
+          <t>job_family_Communications</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1263,13 +1263,13 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>-0.041</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.013</v>
+        <v>-0.002</v>
       </c>
       <c r="E31" t="n">
-        <v>0.028</v>
+        <v>0.006999999999999999</v>
       </c>
       <c r="F31" t="b">
         <v>1</v>
@@ -1281,7 +1281,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>region_Middle_East_and_Africa</t>
+          <t>job_family_Sales</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1290,13 +1290,13 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>-0.066</v>
+        <v>-0.019</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.057</v>
+        <v>-0.023</v>
       </c>
       <c r="E32" t="n">
-        <v>0.009000000000000001</v>
+        <v>-0.004</v>
       </c>
       <c r="F32" t="b">
         <v>1</v>
@@ -1308,7 +1308,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>region_North_America</t>
+          <t>region_Middle_East_and_Africa</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1317,18 +1317,45 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.022</v>
+        <v>-0.066</v>
       </c>
       <c r="D33" t="n">
-        <v>0.015</v>
+        <v>-0.057</v>
       </c>
       <c r="E33" t="n">
-        <v>0.006999999999999999</v>
+        <v>0.009000000000000001</v>
       </c>
       <c r="F33" t="b">
         <v>1</v>
       </c>
       <c r="G33" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>baseline_workload</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>continuous</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>-0.002</v>
+      </c>
+      <c r="D34" t="n">
+        <v>-0.042</v>
+      </c>
+      <c r="E34" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="F34" t="b">
+        <v>1</v>
+      </c>
+      <c r="G34" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1388,22 +1415,22 @@
         <v>7220</v>
       </c>
       <c r="B2" t="n">
-        <v>7094.386718944053</v>
+        <v>7093.805668076424</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9957648995493169</v>
+        <v>0.9958005957981426</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1325095691671194</v>
+        <v>0.1328258918333825</v>
       </c>
       <c r="E2" t="n">
-        <v>1.678870188120527</v>
+        <v>1.685086418270234</v>
       </c>
       <c r="F2" t="n">
-        <v>1.124267686541995</v>
+        <v>1.124755594450756</v>
       </c>
       <c r="G2" t="n">
-        <v>1.678043421071839</v>
+        <v>1.683051778403941</v>
       </c>
     </row>
   </sheetData>
@@ -1464,19 +1491,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.667251009830693</v>
+        <v>1.667057534699058</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1039505645896223</v>
+        <v>0.1039364500786134</v>
       </c>
       <c r="D2" t="n">
-        <v>1.463511647062429</v>
+        <v>1.46334583586403</v>
       </c>
       <c r="E2" t="n">
-        <v>1.870990372598958</v>
+        <v>1.870769233534086</v>
       </c>
       <c r="F2" t="n">
-        <v>6.837236032486468e-58</v>
+        <v>6.802471999971477e-58</v>
       </c>
       <c r="G2" t="n">
         <v>0.05</v>
@@ -1489,19 +1516,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.02463484865352595</v>
+        <v>-0.02459156738062893</v>
       </c>
       <c r="C3" t="n">
-        <v>0.02140527657651924</v>
+        <v>0.02140527432766424</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.06658841982262248</v>
+        <v>-0.06654513414205068</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01731872251557058</v>
+        <v>0.01736199938079281</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2497826842838102</v>
+        <v>0.2506155650116353</v>
       </c>
       <c r="G3" t="n">
         <v>0.05</v>
@@ -1514,19 +1541,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.0754091500964236</v>
+        <v>-0.07551420708983096</v>
       </c>
       <c r="C4" t="n">
-        <v>0.05279509857940829</v>
+        <v>0.05280032846285382</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.1788856418723056</v>
+        <v>-0.1790009492489096</v>
       </c>
       <c r="E4" t="n">
-        <v>0.02806734167945842</v>
+        <v>0.02797253506924763</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1531951152281506</v>
+        <v>0.1526640960983818</v>
       </c>
       <c r="G4" t="n">
         <v>0.05</v>
@@ -1539,19 +1566,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.07777010843832738</v>
+        <v>-0.07779512547504261</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0374666996651623</v>
+        <v>0.03745864396191224</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.1512034904016244</v>
+        <v>-0.1512127185500994</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.004336726475030375</v>
+        <v>-0.004377532399985853</v>
       </c>
       <c r="F5" t="n">
-        <v>0.03792052047519403</v>
+        <v>0.03781752357803483</v>
       </c>
       <c r="G5" t="n">
         <v>0.05</v>
@@ -1564,19 +1591,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.02910393820822508</v>
+        <v>0.02905433458750125</v>
       </c>
       <c r="C6" t="n">
-        <v>0.03598696595065994</v>
+        <v>0.03598413781957191</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.04142921896793762</v>
+        <v>-0.04147327955358536</v>
       </c>
       <c r="E6" t="n">
-        <v>0.09963709538438777</v>
+        <v>0.09958194872858787</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4186672829157758</v>
+        <v>0.4194241955012077</v>
       </c>
       <c r="G6" t="n">
         <v>0.05</v>
@@ -1589,19 +1616,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02381528941209119</v>
+        <v>0.02386878238742906</v>
       </c>
       <c r="C7" t="n">
-        <v>0.03444948165300096</v>
+        <v>0.03444230723095773</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.04370445391386405</v>
+        <v>-0.04363689932971157</v>
       </c>
       <c r="E7" t="n">
-        <v>0.09133503273804644</v>
+        <v>0.09137446410456967</v>
       </c>
       <c r="F7" t="n">
-        <v>0.489370415995682</v>
+        <v>0.4883047508165195</v>
       </c>
       <c r="G7" t="n">
         <v>0.05</v>
@@ -1614,19 +1641,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.03400947065252902</v>
+        <v>0.03407929589427781</v>
       </c>
       <c r="C8" t="n">
-        <v>0.03572753009575888</v>
+        <v>0.03572350274317036</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.03601520159172925</v>
+        <v>-0.03593748288395392</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1040341428967873</v>
+        <v>0.1040960746725095</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3411415276602031</v>
+        <v>0.340096759640682</v>
       </c>
       <c r="G8" t="n">
         <v>0.05</v>
@@ -1639,19 +1666,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.03806830840584247</v>
+        <v>0.0380246395493859</v>
       </c>
       <c r="C9" t="n">
-        <v>0.03435019598273852</v>
+        <v>0.03434053922890857</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.02925683858221748</v>
+        <v>-0.02928158054895977</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1053934553939024</v>
+        <v>0.1053308596477316</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2677575867271219</v>
+        <v>0.2681722936342084</v>
       </c>
       <c r="G9" t="n">
         <v>0.05</v>
@@ -1664,19 +1691,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.002048208353331629</v>
+        <v>0.002108926766444186</v>
       </c>
       <c r="C10" t="n">
-        <v>0.05422289275560438</v>
+        <v>0.05423092905058535</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.1042267085852308</v>
+        <v>-0.1041817410208501</v>
       </c>
       <c r="E10" t="n">
-        <v>0.108323125291894</v>
+        <v>0.1083995945537384</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9698679804037601</v>
+        <v>0.9689797663112278</v>
       </c>
       <c r="G10" t="n">
         <v>0.05</v>
@@ -1689,19 +1716,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.002592226077109182</v>
+        <v>-0.002698318963696233</v>
       </c>
       <c r="C11" t="n">
-        <v>0.05602652915899779</v>
+        <v>0.05603185984561381</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.112402205407528</v>
+        <v>-0.1125187462478953</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1072177532533097</v>
+        <v>0.1071221083205029</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9630967776380733</v>
+        <v>0.9615912234151366</v>
       </c>
       <c r="G11" t="n">
         <v>0.05</v>
@@ -1714,19 +1741,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.09685847877529374</v>
+        <v>-0.09690684290742652</v>
       </c>
       <c r="C12" t="n">
-        <v>0.05376448018771034</v>
+        <v>0.05376611743977986</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.2022349235907233</v>
+        <v>-0.202286496677946</v>
       </c>
       <c r="E12" t="n">
-        <v>0.008517966040135813</v>
+        <v>0.008472810863092914</v>
       </c>
       <c r="F12" t="n">
-        <v>0.07161892986848817</v>
+        <v>0.07148602519025424</v>
       </c>
       <c r="G12" t="n">
         <v>0.05</v>
@@ -1739,19 +1766,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.05872986129122744</v>
+        <v>0.05861966677649856</v>
       </c>
       <c r="C13" t="n">
-        <v>0.05289827688087843</v>
+        <v>0.05290215792217631</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.04494885623952206</v>
+        <v>-0.0450666574554173</v>
       </c>
       <c r="E13" t="n">
-        <v>0.162408578821977</v>
+        <v>0.1623059910084144</v>
       </c>
       <c r="F13" t="n">
-        <v>0.2668949821258334</v>
+        <v>0.2678285440445217</v>
       </c>
       <c r="G13" t="n">
         <v>0.05</v>
@@ -1764,19 +1791,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.01177434185712845</v>
+        <v>0.01179934497704007</v>
       </c>
       <c r="C14" t="n">
-        <v>0.05286151476865345</v>
+        <v>0.05285544422806155</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.09183232325766447</v>
+        <v>-0.09179542209682605</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1153810069719214</v>
+        <v>0.1153941120509062</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8237383381340877</v>
+        <v>0.8233502589464906</v>
       </c>
       <c r="G14" t="n">
         <v>0.05</v>
@@ -1789,19 +1816,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.08022934381684163</v>
+        <v>-0.08024560007397158</v>
       </c>
       <c r="C15" t="n">
-        <v>0.05335891402080917</v>
+        <v>0.05335929880103336</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.1848108935517969</v>
+        <v>-0.1848279039643083</v>
       </c>
       <c r="E15" t="n">
-        <v>0.02435220591811366</v>
+        <v>0.0243367038163651</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1326897956946211</v>
+        <v>0.1326141122249536</v>
       </c>
       <c r="G15" t="n">
         <v>0.05</v>
@@ -1814,19 +1841,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.02854452070261681</v>
+        <v>0.02846031488384166</v>
       </c>
       <c r="C16" t="n">
-        <v>0.05244177820955667</v>
+        <v>0.05244704774958051</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.07423947587335167</v>
+        <v>-0.07433400980078862</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1313285172785853</v>
+        <v>0.1312546395684719</v>
       </c>
       <c r="F16" t="n">
-        <v>0.586229001015238</v>
+        <v>0.5873717984965595</v>
       </c>
       <c r="G16" t="n">
         <v>0.05</v>
@@ -1839,19 +1866,19 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.00953507728863757</v>
+        <v>0.009622939087805983</v>
       </c>
       <c r="C17" t="n">
-        <v>0.05256744027004769</v>
+        <v>0.05256092363330976</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.09349521240011638</v>
+        <v>-0.09339457822764131</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1125653669773915</v>
+        <v>0.1126404564032533</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8560634189937375</v>
+        <v>0.8547339765348235</v>
       </c>
       <c r="G17" t="n">
         <v>0.05</v>
@@ -1864,19 +1891,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.09439860867570243</v>
+        <v>-0.09464919935341422</v>
       </c>
       <c r="C18" t="n">
-        <v>0.05484958712397583</v>
+        <v>0.05485507866520833</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.201901824005587</v>
+        <v>-0.202163177906334</v>
       </c>
       <c r="E18" t="n">
-        <v>0.01310460665418209</v>
+        <v>0.0128647791995056</v>
       </c>
       <c r="F18" t="n">
-        <v>0.08524265511921732</v>
+        <v>0.08444803584756623</v>
       </c>
       <c r="G18" t="n">
         <v>0.05</v>
@@ -1889,19 +1916,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.03376783026243111</v>
+        <v>-0.03392408388401526</v>
       </c>
       <c r="C19" t="n">
-        <v>0.05194237008077476</v>
+        <v>0.0519503019773951</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1355730048924005</v>
+        <v>-0.1357448047456896</v>
       </c>
       <c r="E19" t="n">
-        <v>0.06803734436753828</v>
+        <v>0.06789663697765909</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5156264420353125</v>
+        <v>0.5137496183866248</v>
       </c>
       <c r="G19" t="n">
         <v>0.05</v>
@@ -1914,19 +1941,19 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.02764259828225423</v>
+        <v>-0.02760797148779861</v>
       </c>
       <c r="C20" t="n">
-        <v>0.05243646023149124</v>
+        <v>0.05243884475714464</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1304161718127439</v>
+        <v>-0.1303862186026891</v>
       </c>
       <c r="E20" t="n">
-        <v>0.07513097524823542</v>
+        <v>0.07517027562709191</v>
       </c>
       <c r="F20" t="n">
-        <v>0.598079915706246</v>
+        <v>0.5985551617146732</v>
       </c>
       <c r="G20" t="n">
         <v>0.05</v>
@@ -1939,19 +1966,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-0.05277599238898849</v>
+        <v>-0.0528864761639757</v>
       </c>
       <c r="C21" t="n">
-        <v>0.05170157742489204</v>
+        <v>0.05170437668208597</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.154109222085686</v>
+        <v>-0.1542251923039568</v>
       </c>
       <c r="E21" t="n">
-        <v>0.04855723730770903</v>
+        <v>0.0484522399760054</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3073581670729137</v>
+        <v>0.3063727874189761</v>
       </c>
       <c r="G21" t="n">
         <v>0.05</v>
@@ -1964,19 +1991,19 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.03816573212201323</v>
+        <v>-0.038214533218665</v>
       </c>
       <c r="C22" t="n">
-        <v>0.05200730262192984</v>
+        <v>0.05200529590021602</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1400981721940713</v>
+        <v>-0.1401430401884369</v>
       </c>
       <c r="E22" t="n">
-        <v>0.06376670795004477</v>
+        <v>0.06371397375110693</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4630381345915006</v>
+        <v>0.4624491052692307</v>
       </c>
       <c r="G22" t="n">
         <v>0.05</v>
@@ -1989,19 +2016,19 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.05938706149335556</v>
+        <v>-0.05939396367195356</v>
       </c>
       <c r="C23" t="n">
-        <v>0.05429573538926729</v>
+        <v>0.0543001723142704</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.1658047473704363</v>
+        <v>-0.1658203457622425</v>
       </c>
       <c r="E23" t="n">
-        <v>0.04703062438372518</v>
+        <v>0.04703241841833539</v>
       </c>
       <c r="F23" t="n">
-        <v>0.274055743506363</v>
+        <v>0.2740391883174065</v>
       </c>
       <c r="G23" t="n">
         <v>0.05</v>
@@ -2014,19 +2041,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.008451758672660556</v>
+        <v>0.008554251100005622</v>
       </c>
       <c r="C24" t="n">
-        <v>0.04715478622950785</v>
+        <v>0.04714697844654479</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.08396992403586014</v>
+        <v>-0.08385212863510834</v>
       </c>
       <c r="E24" t="n">
-        <v>0.1008734413811812</v>
+        <v>0.1009606308351196</v>
       </c>
       <c r="F24" t="n">
-        <v>0.8577536728165647</v>
+        <v>0.8560238336771221</v>
       </c>
       <c r="G24" t="n">
         <v>0.05</v>
@@ -2039,19 +2066,19 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.008266388421399316</v>
+        <v>0.008330531317806179</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0261636360193562</v>
+        <v>0.02616718960488387</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.04301339588115374</v>
+        <v>-0.04295621788439709</v>
       </c>
       <c r="E25" t="n">
-        <v>0.05954617272395238</v>
+        <v>0.05961728052000945</v>
       </c>
       <c r="F25" t="n">
-        <v>0.752040818856164</v>
+        <v>0.750213475356229</v>
       </c>
       <c r="G25" t="n">
         <v>0.05</v>
@@ -2064,19 +2091,19 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.02423811373715803</v>
+        <v>0.02424714499797282</v>
       </c>
       <c r="C26" t="n">
-        <v>0.03264857083897001</v>
+        <v>0.03265065717218208</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.03975190925392785</v>
+        <v>-0.03974696713106847</v>
       </c>
       <c r="E26" t="n">
-        <v>0.08822813672824389</v>
+        <v>0.0882412571270141</v>
       </c>
       <c r="F26" t="n">
-        <v>0.4578484564206033</v>
+        <v>0.4577096625377131</v>
       </c>
       <c r="G26" t="n">
         <v>0.05</v>
@@ -2089,19 +2116,19 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.0391593403491267</v>
+        <v>-0.03912913997782917</v>
       </c>
       <c r="C27" t="n">
-        <v>0.03173000514229343</v>
+        <v>0.03172898075157674</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.1013490076572925</v>
+        <v>-0.1013167995170842</v>
       </c>
       <c r="E27" t="n">
-        <v>0.02303032695903913</v>
+        <v>0.02305851956142584</v>
       </c>
       <c r="F27" t="n">
-        <v>0.2171498974623949</v>
+        <v>0.2174898593271097</v>
       </c>
       <c r="G27" t="n">
         <v>0.05</v>
@@ -2114,19 +2141,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.01922954242420746</v>
+        <v>0.01926734751463025</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0322780566849957</v>
+        <v>0.03227922232167944</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.04403428616932643</v>
+        <v>-0.04399876568482283</v>
       </c>
       <c r="E28" t="n">
-        <v>0.08249337101774136</v>
+        <v>0.08253346071408332</v>
       </c>
       <c r="F28" t="n">
-        <v>0.5513445242495123</v>
+        <v>0.5505766354403396</v>
       </c>
       <c r="G28" t="n">
         <v>0.05</v>
@@ -2139,19 +2166,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.06730170037260196</v>
+        <v>0.06728645489710121</v>
       </c>
       <c r="C29" t="n">
-        <v>0.03196767543970735</v>
+        <v>0.03196900488547524</v>
       </c>
       <c r="D29" t="n">
-        <v>0.004646207841309924</v>
+        <v>0.004628356699984695</v>
       </c>
       <c r="E29" t="n">
-        <v>0.129957192903894</v>
+        <v>0.1299445530942177</v>
       </c>
       <c r="F29" t="n">
-        <v>0.0352647850385131</v>
+        <v>0.03531391507082924</v>
       </c>
       <c r="G29" t="n">
         <v>0.05</v>
@@ -2164,19 +2191,19 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.0405928052277169</v>
+        <v>-0.04071597969725242</v>
       </c>
       <c r="C30" t="n">
-        <v>0.04219295914182773</v>
+        <v>0.04219485817141799</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.1232894855468693</v>
+        <v>-0.1234163820460073</v>
       </c>
       <c r="E30" t="n">
-        <v>0.04210387509143548</v>
+        <v>0.04198442265150244</v>
       </c>
       <c r="F30" t="n">
-        <v>0.3360117637295972</v>
+        <v>0.3345692469681957</v>
       </c>
       <c r="G30" t="n">
         <v>0.05</v>
@@ -2185,23 +2212,23 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>is_new_manager</t>
+          <t>baseline_workload</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.02814404589903955</v>
+        <v>0.4490720848345699</v>
       </c>
       <c r="C31" t="n">
-        <v>0.02420739120983631</v>
+        <v>0.01068359759505054</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.07558966082999022</v>
+        <v>0.4281326183229521</v>
       </c>
       <c r="E31" t="n">
-        <v>0.01930156903191111</v>
+        <v>0.4700115513461877</v>
       </c>
       <c r="F31" t="n">
-        <v>0.2449828954760783</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
         <v>0.05</v>
@@ -2210,23 +2237,23 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>baseline_workload</t>
+          <t>is_new_manager</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.4490526515310966</v>
+        <v>-0.02815956548344896</v>
       </c>
       <c r="C32" t="n">
-        <v>0.01068393144388238</v>
+        <v>0.02420948131337568</v>
       </c>
       <c r="D32" t="n">
-        <v>0.4281125306877921</v>
+        <v>-0.07560927694206074</v>
       </c>
       <c r="E32" t="n">
-        <v>0.4699927723744011</v>
+        <v>0.01929014597516282</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>0.2447634997487514</v>
       </c>
       <c r="G32" t="n">
         <v>0.05</v>
@@ -2239,19 +2266,19 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.003364288003062581</v>
+        <v>0.003368127275367436</v>
       </c>
       <c r="C33" t="n">
-        <v>0.001764656162787883</v>
+        <v>0.001764528679284788</v>
       </c>
       <c r="D33" t="n">
-        <v>-9.437452109831981e-05</v>
+        <v>-9.028538571877664e-05</v>
       </c>
       <c r="E33" t="n">
-        <v>0.006822950527223481</v>
+        <v>0.006826539936453649</v>
       </c>
       <c r="F33" t="n">
-        <v>0.05658749372658183</v>
+        <v>0.05628826750556205</v>
       </c>
       <c r="G33" t="n">
         <v>0.05</v>
@@ -2264,19 +2291,19 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.0009948915328936501</v>
+        <v>-0.0009920422931855091</v>
       </c>
       <c r="C34" t="n">
-        <v>0.00157771174042372</v>
+        <v>0.001578082718395982</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.004087149722110148</v>
+        <v>-0.004085027585866699</v>
       </c>
       <c r="E34" t="n">
-        <v>0.002097366656322847</v>
+        <v>0.00210094299949568</v>
       </c>
       <c r="F34" t="n">
-        <v>0.5283076912308</v>
+        <v>0.5295862719421289</v>
       </c>
       <c r="G34" t="n">
         <v>0.05</v>
@@ -2289,19 +2316,19 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3.375687514584298e-05</v>
+        <v>3.065588116314876e-05</v>
       </c>
       <c r="C35" t="n">
-        <v>0.004788621486128021</v>
+        <v>0.004788074446685936</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.00935176877325975</v>
+        <v>-0.009353797589637834</v>
       </c>
       <c r="E35" t="n">
-        <v>0.009419282523551434</v>
+        <v>0.009415109351964131</v>
       </c>
       <c r="F35" t="n">
-        <v>0.9943754446863978</v>
+        <v>0.9948915399209103</v>
       </c>
       <c r="G35" t="n">
         <v>0.05</v>
@@ -2314,19 +2341,19 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.001861597274177134</v>
+        <v>0.001858686570725001</v>
       </c>
       <c r="C36" t="n">
-        <v>0.001577846052651468</v>
+        <v>0.001577825229323155</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.001230924162168433</v>
+        <v>-0.001233794052647035</v>
       </c>
       <c r="E36" t="n">
-        <v>0.0049541187105227</v>
+        <v>0.004951167194097037</v>
       </c>
       <c r="F36" t="n">
-        <v>0.2380660284989632</v>
+        <v>0.238794471048539</v>
       </c>
       <c r="G36" t="n">
         <v>0.05</v>
@@ -2343,7 +2370,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2375,13 +2402,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-2.680600179802939</v>
+        <v>-2.713407322158417</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4771933030981503</v>
+        <v>0.5044376034036473</v>
       </c>
       <c r="D2" t="n">
-        <v>1.938181768273511e-08</v>
+        <v>7.486982883646451e-08</v>
       </c>
     </row>
     <row r="3">
@@ -2391,13 +2418,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.02542074333516161</v>
+        <v>-0.02522051520904557</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1002143663033998</v>
+        <v>0.1001657906734904</v>
       </c>
       <c r="D3" t="n">
-        <v>0.79975540801217</v>
+        <v>0.80120515614857</v>
       </c>
     </row>
     <row r="4">
@@ -2407,13 +2434,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2244463748843409</v>
+        <v>0.2243950733516431</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2335027157442915</v>
+        <v>0.2334051881144239</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3364439424069162</v>
+        <v>0.3363525367569156</v>
       </c>
     </row>
     <row r="5">
@@ -2423,13 +2450,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8155080917228588</v>
+        <v>0.8152523591729706</v>
       </c>
       <c r="C5" t="n">
-        <v>0.173402651392118</v>
+        <v>0.173290598705334</v>
       </c>
       <c r="D5" t="n">
-        <v>2.563995828054386e-06</v>
+        <v>2.544403764026845e-06</v>
       </c>
     </row>
     <row r="6">
@@ -2439,13 +2466,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.03527526670387308</v>
+        <v>0.03529662509742176</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1916882946919544</v>
+        <v>0.1917359483069559</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8539945454713548</v>
+        <v>0.853943037936749</v>
       </c>
     </row>
     <row r="7">
@@ -2455,13 +2482,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2773648159307716</v>
+        <v>0.2770307728862446</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1901447102133385</v>
+        <v>0.1900876275228707</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1446466431125523</v>
+        <v>0.1450102574315858</v>
       </c>
     </row>
     <row r="8">
@@ -2471,13 +2498,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1036811851537241</v>
+        <v>0.103322246136425</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1952515666982444</v>
+        <v>0.1951486965374491</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5954095400432469</v>
+        <v>0.5964905887803367</v>
       </c>
     </row>
     <row r="9">
@@ -2487,13 +2514,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8738774480300985</v>
+        <v>0.8739030378849018</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1695280942409139</v>
+        <v>0.1695379888770779</v>
       </c>
       <c r="D9" t="n">
-        <v>2.539495077342821e-07</v>
+        <v>2.541527320496806e-07</v>
       </c>
     </row>
     <row r="10">
@@ -2503,13 +2530,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.0445652077261707</v>
+        <v>-0.04298175525170801</v>
       </c>
       <c r="C10" t="n">
-        <v>0.260402103171632</v>
+        <v>0.2597533292652202</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8641137091517843</v>
+        <v>0.8685729341423538</v>
       </c>
     </row>
     <row r="11">
@@ -2519,13 +2546,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.2737623724798146</v>
+        <v>-0.273477418337526</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2787881385465067</v>
+        <v>0.2785592488643232</v>
       </c>
       <c r="D11" t="n">
-        <v>0.326113242387764</v>
+        <v>0.3262197079678815</v>
       </c>
     </row>
     <row r="12">
@@ -2535,13 +2562,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.08100487957118148</v>
+        <v>0.08217580196393665</v>
       </c>
       <c r="C12" t="n">
-        <v>0.2596429772097172</v>
+        <v>0.2587287215011224</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7550514391424692</v>
+        <v>0.7507779355278769</v>
       </c>
     </row>
     <row r="13">
@@ -2551,13 +2578,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.03917827337461754</v>
+        <v>0.03995788006654466</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2572958805743774</v>
+        <v>0.2568297818201685</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8789745077123743</v>
+        <v>0.8763631618417507</v>
       </c>
     </row>
     <row r="14">
@@ -2567,13 +2594,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.05296103812307935</v>
+        <v>-0.05219347665549049</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2610089865588724</v>
+        <v>0.260344375550927</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8392062624375534</v>
+        <v>0.8411062907988971</v>
       </c>
     </row>
     <row r="15">
@@ -2583,13 +2610,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1181322726534161</v>
+        <v>0.1183975653249727</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2572294350577187</v>
+        <v>0.2570359266688497</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6460556128984086</v>
+        <v>0.6450665788994057</v>
       </c>
     </row>
     <row r="16">
@@ -2599,13 +2626,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.004000986240379481</v>
+        <v>-0.002815011182394687</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2383903410311192</v>
+        <v>0.2376522981116131</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9866094604655132</v>
+        <v>0.9905492122003384</v>
       </c>
     </row>
     <row r="17">
@@ -2615,13 +2642,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.1057185310395306</v>
+        <v>0.1056709152111879</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2543340222421759</v>
+        <v>0.2542906688395364</v>
       </c>
       <c r="D17" t="n">
-        <v>0.677652912256731</v>
+        <v>0.6777380893434587</v>
       </c>
     </row>
     <row r="18">
@@ -2631,13 +2658,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.1377694895733254</v>
+        <v>-0.1371135645044842</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2636874203313636</v>
+        <v>0.2634072330241231</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6013412201546282</v>
+        <v>0.6026884109023536</v>
       </c>
     </row>
     <row r="19">
@@ -2647,13 +2674,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.02557154094223237</v>
+        <v>-0.02475228489410927</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2527597901538116</v>
+        <v>0.2524092973060099</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9194160355966677</v>
+        <v>0.9218814119969652</v>
       </c>
     </row>
     <row r="20">
@@ -2663,13 +2690,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.07344622569376411</v>
+        <v>-0.07246351166486148</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2674578609541021</v>
+        <v>0.2666987121614959</v>
       </c>
       <c r="D20" t="n">
-        <v>0.7836169672222787</v>
+        <v>0.7858484583220696</v>
       </c>
     </row>
     <row r="21">
@@ -2679,13 +2706,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.2063167170305062</v>
+        <v>0.2068090257965713</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2442896532450728</v>
+        <v>0.2439533267288626</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3983578134719854</v>
+        <v>0.3965827100652908</v>
       </c>
     </row>
     <row r="22">
@@ -2695,13 +2722,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.1704634573362028</v>
+        <v>-0.1686288808585502</v>
       </c>
       <c r="C22" t="n">
-        <v>0.269674845496591</v>
+        <v>0.2694061394634711</v>
       </c>
       <c r="D22" t="n">
-        <v>0.5273167196806365</v>
+        <v>0.5313620833011139</v>
       </c>
     </row>
     <row r="23">
@@ -2711,13 +2738,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.5008110927334755</v>
+        <v>-0.4997770753001374</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2870672180445716</v>
+        <v>0.2864601345898818</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0810583897517186</v>
+        <v>0.08104313551548854</v>
       </c>
     </row>
     <row r="24">
@@ -2727,13 +2754,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.9366864721074268</v>
+        <v>0.9365913375115046</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1483430409733375</v>
+        <v>0.1482811706186312</v>
       </c>
       <c r="D24" t="n">
-        <v>2.713396260923871e-10</v>
+        <v>2.678649464267732e-10</v>
       </c>
     </row>
     <row r="25">
@@ -2743,13 +2770,13 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.5776106069409677</v>
+        <v>-0.5782787024565067</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1143619392421806</v>
+        <v>0.1145314111910344</v>
       </c>
       <c r="D25" t="n">
-        <v>4.401383208103854e-07</v>
+        <v>4.43933787929666e-07</v>
       </c>
     </row>
     <row r="26">
@@ -2759,13 +2786,13 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.2373161448441742</v>
+        <v>0.2379613006187489</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1503781926377481</v>
+        <v>0.1503209475356382</v>
       </c>
       <c r="D26" t="n">
-        <v>0.1145360411757815</v>
+        <v>0.1134165507753398</v>
       </c>
     </row>
     <row r="27">
@@ -2775,13 +2802,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.04350476117998643</v>
+        <v>-0.04352683570925985</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1611879340386415</v>
+        <v>0.1612096759797175</v>
       </c>
       <c r="D27" t="n">
-        <v>0.7872365295400221</v>
+        <v>0.7871591884734985</v>
       </c>
     </row>
     <row r="28">
@@ -2791,13 +2818,13 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.07514354096975739</v>
+        <v>-0.07467572557157258</v>
       </c>
       <c r="C28" t="n">
-        <v>0.1613683918223571</v>
+        <v>0.1614290026159799</v>
       </c>
       <c r="D28" t="n">
-        <v>0.6414556246120158</v>
+        <v>0.6436570199176094</v>
       </c>
     </row>
     <row r="29">
@@ -2807,93 +2834,109 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.09749293462742094</v>
+        <v>0.09777326958921113</v>
       </c>
       <c r="C29" t="n">
-        <v>0.1543265796290169</v>
+        <v>0.1543602583723146</v>
       </c>
       <c r="D29" t="n">
-        <v>0.5275624553510021</v>
+        <v>0.5264661972233937</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>is_new_manager</t>
+          <t>baseline_workload</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.2280638724458788</v>
+        <v>0.01034291492939445</v>
       </c>
       <c r="C30" t="n">
-        <v>0.1146565719927948</v>
+        <v>0.05138615505935807</v>
       </c>
       <c r="D30" t="n">
-        <v>0.04668969945129902</v>
+        <v>0.8404810151443465</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>age</t>
+          <t>is_new_manager</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.005012017390962181</v>
+        <v>0.2275650381150178</v>
       </c>
       <c r="C31" t="n">
-        <v>0.008304876992454899</v>
+        <v>0.114454928387682</v>
       </c>
       <c r="D31" t="n">
-        <v>0.5461741835341518</v>
+        <v>0.04678402178782443</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>tenure_months</t>
+          <t>age</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.002418133412192865</v>
+        <v>-0.004998614827289092</v>
       </c>
       <c r="C32" t="n">
-        <v>0.007135781003458533</v>
+        <v>0.008307994570919576</v>
       </c>
       <c r="D32" t="n">
-        <v>0.7347043603418282</v>
+        <v>0.5473983322894189</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>num_direct_reports</t>
+          <t>tenure_months</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.004129656026475429</v>
+        <v>-0.002450883409209256</v>
       </c>
       <c r="C33" t="n">
-        <v>0.02222260881033176</v>
+        <v>0.007127711187841278</v>
       </c>
       <c r="D33" t="n">
-        <v>0.8525770672961277</v>
+        <v>0.7309569941465295</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>num_direct_reports</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>-0.004172683243731389</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.02223526945739764</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.851142745037714</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
           <t>tot_span_of_control</t>
         </is>
       </c>
-      <c r="B34" t="n">
-        <v>0.006335499136474494</v>
-      </c>
-      <c r="C34" t="n">
-        <v>0.006871422968197173</v>
-      </c>
-      <c r="D34" t="n">
-        <v>0.3565249957666431</v>
+      <c r="B35" t="n">
+        <v>0.006367932838418616</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.006881672701727231</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0.3547856158497277</v>
       </c>
     </row>
   </sheetData>
